--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral-ecs.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral-ecs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,8 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">
-このプロファイルはDiagnosticReportリソースに対して、診療情報提供書（口腔所見）のデータを送受信するための制約と拡張を定めたものである。</t>
+    <t>このプロファイルはDiagnosticReportリソースに対して、診療情報提供書（口腔所見）のデータを送受信するための制約と拡張を定めたものである。</t>
   </si>
   <si>
     <t>Purpose</t>
